--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/273FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/273FL_10A.xlsx
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
